--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N76_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N76_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>54.94772514338617</v>
+        <v>8.929005335800252</v>
       </c>
       <c r="D2" t="n">
-        <v>55.29554353741685</v>
+        <v>8.985525824830239</v>
       </c>
       <c r="E2" t="n">
-        <v>7.969666569971364</v>
+        <v>1.295070817620347</v>
       </c>
       <c r="F2" t="n">
-        <v>13.78527457257808</v>
+        <v>2.240107118043938</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>37.57217046850688</v>
+        <v>6.105477701132369</v>
       </c>
       <c r="D3" t="n">
-        <v>37.92427648357295</v>
+        <v>6.162694928580604</v>
       </c>
       <c r="E3" t="n">
-        <v>7.969666569971364</v>
+        <v>1.295070817620347</v>
       </c>
       <c r="F3" t="n">
-        <v>13.78527457257808</v>
+        <v>2.240107118043938</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>42.63733692250465</v>
+        <v>6.928567249907006</v>
       </c>
       <c r="D4" t="n">
-        <v>43.00671725875671</v>
+        <v>6.988591554547965</v>
       </c>
       <c r="E4" t="n">
-        <v>7.969666569971364</v>
+        <v>1.295070817620347</v>
       </c>
       <c r="F4" t="n">
-        <v>13.78527457257808</v>
+        <v>2.240107118043938</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>39.48209558186652</v>
+        <v>6.41584053205331</v>
       </c>
       <c r="D5" t="n">
-        <v>39.72782834365091</v>
+        <v>6.455772105843273</v>
       </c>
       <c r="E5" t="n">
-        <v>7.969666569971364</v>
+        <v>1.295070817620347</v>
       </c>
       <c r="F5" t="n">
-        <v>13.78527457257808</v>
+        <v>2.240107118043938</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>26.94842864494994</v>
+        <v>4.379119654804366</v>
       </c>
       <c r="D6" t="n">
-        <v>27.23025002606551</v>
+        <v>4.424915629235645</v>
       </c>
       <c r="E6" t="n">
-        <v>7.969666569971364</v>
+        <v>1.295070817620347</v>
       </c>
       <c r="F6" t="n">
-        <v>13.78527457257808</v>
+        <v>2.240107118043938</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>36.16068265345799</v>
+        <v>5.876110931186924</v>
       </c>
       <c r="D7" t="n">
-        <v>36.05840382518435</v>
+        <v>5.859490621592457</v>
       </c>
       <c r="E7" t="n">
-        <v>7.969666569971364</v>
+        <v>1.295070817620347</v>
       </c>
       <c r="F7" t="n">
-        <v>13.78527457257808</v>
+        <v>2.240107118043938</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>33.65524684084465</v>
+        <v>5.468977611637255</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79995444861687</v>
+        <v>5.492492597900242</v>
       </c>
       <c r="E8" t="n">
-        <v>7.969666569971364</v>
+        <v>1.295070817620347</v>
       </c>
       <c r="F8" t="n">
-        <v>13.78527457257808</v>
+        <v>2.240107118043938</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>46.46986437621383</v>
+        <v>7.551352961134747</v>
       </c>
       <c r="D9" t="n">
-        <v>47.38222344173187</v>
+        <v>7.69961130928143</v>
       </c>
       <c r="E9" t="n">
-        <v>7.969666569971364</v>
+        <v>1.295070817620347</v>
       </c>
       <c r="F9" t="n">
-        <v>13.78527457257808</v>
+        <v>2.240107118043938</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>22.52256151988203</v>
+        <v>3.659916246980829</v>
       </c>
       <c r="D10" t="n">
-        <v>21.37759904430096</v>
+        <v>3.473859844698906</v>
       </c>
       <c r="E10" t="n">
-        <v>7.969666569971364</v>
+        <v>1.295070817620347</v>
       </c>
       <c r="F10" t="n">
-        <v>13.78527457257808</v>
+        <v>2.240107118043938</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>44.49375988442093</v>
+        <v>7.230235981218402</v>
       </c>
       <c r="D11" t="n">
-        <v>34.45128973401882</v>
+        <v>5.598334581778059</v>
       </c>
       <c r="E11" t="n">
-        <v>7.969666569971364</v>
+        <v>1.295070817620347</v>
       </c>
       <c r="F11" t="n">
-        <v>13.78527457257808</v>
+        <v>2.240107118043938</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>35.44457728205141</v>
+        <v>5.759743808333353</v>
       </c>
       <c r="D12" t="n">
-        <v>15.53764433124718</v>
+        <v>2.524867203827666</v>
       </c>
       <c r="E12" t="n">
-        <v>7.969666569971364</v>
+        <v>1.295070817620347</v>
       </c>
       <c r="F12" t="n">
-        <v>13.78527457257808</v>
+        <v>2.240107118043938</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>42.23907361168072</v>
+        <v>6.863849461898116</v>
       </c>
       <c r="D13" t="n">
-        <v>17.28384952571043</v>
+        <v>2.808625547927944</v>
       </c>
       <c r="E13" t="n">
-        <v>7.969666569971364</v>
+        <v>1.295070817620347</v>
       </c>
       <c r="F13" t="n">
-        <v>13.78527457257808</v>
+        <v>2.240107118043938</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>44.56258748206342</v>
+        <v>7.241420465835306</v>
       </c>
       <c r="D14" t="n">
-        <v>13.27072285363654</v>
+        <v>2.156492463715937</v>
       </c>
       <c r="E14" t="n">
-        <v>7.969666569971364</v>
+        <v>1.295070817620347</v>
       </c>
       <c r="F14" t="n">
-        <v>13.78527457257808</v>
+        <v>2.240107118043938</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>46.17213640213023</v>
+        <v>7.502972165346163</v>
       </c>
       <c r="D15" t="n">
-        <v>10.74109370907079</v>
+        <v>1.745427727724003</v>
       </c>
       <c r="E15" t="n">
-        <v>7.969666569971364</v>
+        <v>1.295070817620347</v>
       </c>
       <c r="F15" t="n">
-        <v>13.78527457257808</v>
+        <v>2.240107118043938</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>46.21809281405201</v>
+        <v>7.510440082283452</v>
       </c>
       <c r="D16" t="n">
-        <v>9.733586989833785</v>
+        <v>1.58170788584799</v>
       </c>
       <c r="E16" t="n">
-        <v>7.969666569971364</v>
+        <v>1.295070817620347</v>
       </c>
       <c r="F16" t="n">
-        <v>13.78527457257808</v>
+        <v>2.240107118043938</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
